--- a/01_Thermal/B_results/four_annular_var_params.xlsx
+++ b/01_Thermal/B_results/four_annular_var_params.xlsx
@@ -541,64 +541,64 @@
         <v>0.2</v>
       </c>
       <c r="B2" t="n">
-        <v>9.198676639139755</v>
+        <v>9.344428292875259</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2872541201410848</v>
+        <v>0.2862253642054461</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1630825379591276</v>
+        <v>0.1624416018005918</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07666690673329439</v>
+        <v>0.07541454071275144</v>
       </c>
       <c r="F2" t="n">
-        <v>7.598691396181825</v>
+        <v>7.608844786840232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2998670595743034</v>
+        <v>0.2996560358148768</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1736381894530776</v>
+        <v>0.1738869456275669</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02518368038800308</v>
+        <v>-0.02997193339580089</v>
       </c>
       <c r="J2" t="n">
-        <v>9.609422979073306</v>
+        <v>9.696242831655457</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2756595145817506</v>
+        <v>0.2750214634047274</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1560049801233156</v>
+        <v>0.1557170303792</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01795065675088793</v>
+        <v>0.01789172514169475</v>
       </c>
       <c r="N2" t="n">
-        <v>9.756380621065565</v>
+        <v>10.11493088203228</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2866424168747286</v>
+        <v>0.2841831323093723</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1653847467304378</v>
+        <v>0.1632747516418727</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1553882530336529</v>
+        <v>0.1553623581017907</v>
       </c>
       <c r="R2" t="n">
-        <v>9.830211560238327</v>
+        <v>9.957694670973066</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2868474895335565</v>
+        <v>0.2860408252928081</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1573022355296795</v>
+        <v>0.1568876795537276</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1585123975366398</v>
+        <v>0.1583760130033212</v>
       </c>
     </row>
     <row r="3">
@@ -606,64 +606,64 @@
         <v>0.35</v>
       </c>
       <c r="B3" t="n">
-        <v>3.715327307204904</v>
+        <v>3.753778586301196</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2979115499947765</v>
+        <v>0.3254493477119522</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3336350733970882</v>
+        <v>0.2699657371945505</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05268698501985412</v>
+        <v>0.06511331986030697</v>
       </c>
       <c r="F3" t="n">
-        <v>2.176666186727044</v>
+        <v>2.561053877362675</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2304115894974248</v>
+        <v>0.3460891989125424</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6065558057743674</v>
+        <v>0.3465170212640684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09027126322907576</v>
+        <v>0.09928923462332787</v>
       </c>
       <c r="J3" t="n">
-        <v>3.282861387801847</v>
+        <v>3.053007835253892</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3499508676120451</v>
+        <v>0.3476900202304452</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2766619343130752</v>
+        <v>0.2917233338201538</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01659258161355798</v>
+        <v>0.004816020600518427</v>
       </c>
       <c r="N3" t="n">
-        <v>4.812707877648808</v>
+        <v>4.841123574876254</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3103496222036311</v>
+        <v>0.3069259372674192</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2372107278881861</v>
+        <v>0.2314386264468345</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02907170310217727</v>
+        <v>0.03840531207481299</v>
       </c>
       <c r="R3" t="n">
-        <v>4.589073776641919</v>
+        <v>4.559929057711961</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3009341206660053</v>
+        <v>0.3010922344374024</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2141118256127242</v>
+        <v>0.2101839672471455</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1079975553617214</v>
+        <v>0.1179427121425686</v>
       </c>
     </row>
     <row r="4">
@@ -671,64 +671,64 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n">
-        <v>2.384872482823412</v>
+        <v>2.366057855013973</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3814656957315016</v>
+        <v>0.3786960083939125</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3382143252434714</v>
+        <v>0.3215274513974399</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05151551083768401</v>
+        <v>0.064962097924794</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2041564388787</v>
+        <v>2.180678334151925</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5233059709931477</v>
+        <v>0.5231713553554638</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2356541206202205</v>
+        <v>0.2209884291205808</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03587189794542374</v>
+        <v>0.06789182038015565</v>
       </c>
       <c r="J4" t="n">
-        <v>2.322870472751225</v>
+        <v>2.271248836048079</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3434962577202982</v>
+        <v>0.3399371481232145</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3521188271692227</v>
+        <v>0.3395633599827919</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05352925994725392</v>
+        <v>-0.09355808686923892</v>
       </c>
       <c r="N4" t="n">
-        <v>2.558765930038298</v>
+        <v>2.551536371212431</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3328736749951531</v>
+        <v>0.3293035915662078</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3944635423748522</v>
+        <v>0.3760477691781257</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08009475735466268</v>
+        <v>0.1104136260628145</v>
       </c>
       <c r="R4" t="n">
-        <v>2.453697089625424</v>
+        <v>2.460767878643457</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3261868792174077</v>
+        <v>0.3223719385307638</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3706208108095903</v>
+        <v>0.3495102473082614</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1436246479979036</v>
+        <v>0.1751010321254448</v>
       </c>
     </row>
     <row r="5">
@@ -736,64 +736,64 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n">
-        <v>2.645704906928875</v>
+        <v>2.654855531540862</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5057845137098679</v>
+        <v>0.5053821075001481</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2463982842020314</v>
+        <v>0.2537781750380912</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08951081109829766</v>
+        <v>0.08355179200659028</v>
       </c>
       <c r="F5" t="n">
-        <v>2.852764430904731</v>
+        <v>2.87524741743628</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5756831246121202</v>
+        <v>0.5772429039286974</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1945110615634391</v>
+        <v>0.1970324527139822</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9832692074362903</v>
+        <v>-0.5142106149879934</v>
       </c>
       <c r="J5" t="n">
-        <v>2.838036470005195</v>
+        <v>2.867459062131027</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5814670877657953</v>
+        <v>0.5815544610245257</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1924228727314873</v>
+        <v>0.1950433476218315</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4092081577844228</v>
+        <v>0.2190275319738828</v>
       </c>
       <c r="N5" t="n">
-        <v>2.394316362549987</v>
+        <v>2.40216503248121</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3258758161427733</v>
+        <v>0.327844840874757</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3788109809280889</v>
+        <v>0.3895127412133397</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4298812595758854</v>
+        <v>0.2796803466147222</v>
       </c>
       <c r="R5" t="n">
-        <v>2.497702364255586</v>
+        <v>2.474550614114928</v>
       </c>
       <c r="S5" t="n">
-        <v>0.540112026318783</v>
+        <v>0.5348862241726122</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2198482215851101</v>
+        <v>0.2335241586032114</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5022230344691727</v>
+        <v>0.3497099044257495</v>
       </c>
     </row>
     <row r="6">
@@ -801,64 +801,64 @@
         <v>1.1</v>
       </c>
       <c r="B6" t="n">
-        <v>1.74401855732209</v>
+        <v>1.730642286748588</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3366238241511047</v>
+        <v>0.3954343663143721</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6331909734884641</v>
+        <v>0.5177991551009251</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02911937593082523</v>
+        <v>0.05181714406754424</v>
       </c>
       <c r="F6" t="n">
-        <v>2.142944443862026</v>
+        <v>2.045540056334477</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3944386771235031</v>
+        <v>0.3979302126516111</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4300343112424942</v>
+        <v>0.4253986366977328</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04403659250013241</v>
+        <v>0.3864121458392175</v>
       </c>
       <c r="J6" t="n">
-        <v>1.602124257554197</v>
+        <v>1.760463919061846</v>
       </c>
       <c r="K6" t="n">
-        <v>0.15</v>
+        <v>0.3819658102075006</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9387386645173901</v>
+        <v>0.5326960651122985</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1630721204788501</v>
+        <v>-0.9879556752717206</v>
       </c>
       <c r="N6" t="n">
-        <v>1.362530394894961</v>
+        <v>1.289915641653443</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4684052910540695</v>
+        <v>0.4675551572777008</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7129938126474523</v>
+        <v>0.6860996075123673</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0598898499833929</v>
+        <v>0.3433499032751084</v>
       </c>
       <c r="R6" t="n">
-        <v>1.868475132977176</v>
+        <v>1.826649529944585</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3336513284268463</v>
+        <v>0.3342862851206758</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4509971055465196</v>
+        <v>0.427002311081302</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1756231817186257</v>
+        <v>0.4654622024275716</v>
       </c>
     </row>
     <row r="7">
@@ -866,64 +866,64 @@
         <v>1.6</v>
       </c>
       <c r="B7" t="n">
-        <v>1.479549004924591</v>
+        <v>1.471807945021149</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2428496067818824</v>
+        <v>0.238180424821621</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6782663030137023</v>
+        <v>0.703941181395799</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03270659404401784</v>
+        <v>0.02880713942981006</v>
       </c>
       <c r="F7" t="n">
-        <v>1.663009919281188</v>
+        <v>1.666673776556509</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3901381817981563</v>
+        <v>0.3900399877079029</v>
       </c>
       <c r="H7" t="n">
-        <v>0.473887973746123</v>
+        <v>0.4832960946418587</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1914515162062064</v>
+        <v>-0.09177067112295376</v>
       </c>
       <c r="J7" t="n">
-        <v>1.295550394953946</v>
+        <v>1.290345189130354</v>
       </c>
       <c r="K7" t="n">
         <v>0.15</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9757739317846694</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2279153534975918</v>
+        <v>-0.1324035721951874</v>
       </c>
       <c r="N7" t="n">
-        <v>1.302964028307335</v>
+        <v>1.292736580598969</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2812602453293731</v>
+        <v>0.2626817115785811</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6457587657966248</v>
+        <v>0.6956057097884215</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2409754070128431</v>
+        <v>0.1416112285191772</v>
       </c>
       <c r="R7" t="n">
-        <v>1.656671677155892</v>
+        <v>1.637476233798765</v>
       </c>
       <c r="S7" t="n">
         <v>0.15</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6176445407273915</v>
+        <v>0.6368629211529162</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3092178388670265</v>
+        <v>0.1977915725182042</v>
       </c>
     </row>
     <row r="8">
@@ -931,31 +931,31 @@
         <v>2.2</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9002915747575302</v>
+        <v>0.8959492238099109</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4965060020743003</v>
+        <v>0.4832352667623759</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7393579215291157</v>
+        <v>0.7557469533045313</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02823476797607735</v>
+        <v>0.02950725840111156</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8775944370541729</v>
+        <v>0.8526467593257749</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4227014205639817</v>
+        <v>0.3781153390750178</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7543384697611446</v>
+        <v>0.8581572316658199</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06252023756852736</v>
+        <v>0.06918838800750286</v>
       </c>
       <c r="J8" t="n">
-        <v>0.620452746137134</v>
+        <v>0.6007230968133103</v>
       </c>
       <c r="K8" t="n">
         <v>0.9499999999999998</v>
@@ -964,31 +964,31 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.04209024883587229</v>
+        <v>-0.04691013832116315</v>
       </c>
       <c r="N8" t="n">
-        <v>1.083693208930535</v>
+        <v>1.124831025203706</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4633225877332194</v>
+        <v>0.4548257279744862</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6518542219368029</v>
+        <v>0.6104306426901321</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.05432561133114995</v>
+        <v>-0.05817172100171421</v>
       </c>
       <c r="R8" t="n">
-        <v>1.019425906908279</v>
+        <v>1.005596013896852</v>
       </c>
       <c r="S8" t="n">
         <v>0.15</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5512389944185154</v>
+        <v>0.5543999388621732</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1468346945028043</v>
+        <v>0.1539225049198207</v>
       </c>
     </row>
   </sheetData>
@@ -1098,10 +1098,10 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3260765801304227</v>
+        <v>0.357225915368531</v>
       </c>
       <c r="G2" t="n">
-        <v>112.1822653355146</v>
+        <v>110.6229071905429</v>
       </c>
       <c r="H2" t="n">
         <v>357</v>
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4538428014899809</v>
+        <v>0.3877359864932275</v>
       </c>
       <c r="G3" t="n">
-        <v>95.44552126461816</v>
+        <v>95.02532262698016</v>
       </c>
       <c r="H3" t="n">
         <v>315</v>
@@ -1198,10 +1198,10 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4340802695733744</v>
+        <v>0.3693997724199814</v>
       </c>
       <c r="G4" t="n">
-        <v>114.6279867934063</v>
+        <v>114.821897545579</v>
       </c>
       <c r="H4" t="n">
         <v>371</v>
@@ -1248,10 +1248,10 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3422376922021006</v>
+        <v>0.3574584826727098</v>
       </c>
       <c r="G5" t="n">
-        <v>94.00577457704249</v>
+        <v>93.9589160210013</v>
       </c>
       <c r="H5" t="n">
         <v>322</v>
